--- a/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Collegetown_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Collegetown_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,190 +524,169 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>004015</t>
+          <t>HS103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Natalie's - Strawberry Lemonade</t>
+          <t>Harney &amp; Sons - REST</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10.25</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>10.25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>004038</t>
+          <t>HS105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Natalie's - Orange Mango</t>
+          <t>Harney &amp; Sons - CRUISE</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>004039</t>
+          <t>004019</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Natalie's - Orange Pineapple</t>
+          <t>Natalie's - Guava Lemonade (12oz)</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10.45</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>004011</t>
+          <t>001023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natalie's - Lemonade</t>
+          <t>Ithaca Yogurt - Vanilla</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>10.25</v>
+        <v>14.5</v>
       </c>
       <c r="E11" t="n">
-        <v>10.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HS103</t>
+          <t>001025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Harney &amp; Sons - REST</t>
+          <t>Ithaca Yogurt - Black Cherry</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HS105</t>
+          <t>004038</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Harney &amp; Sons - CRUISE</t>
+          <t>Natalie's - Orange Mango</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>004019</t>
+          <t>004039</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Natalie's - Guava Lemonade (12oz)</t>
+          <t>Natalie's - Orange Pineapple</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.45</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>10.45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>001023</t>
+          <t>004011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ithaca Yogurt - Vanilla</t>
+          <t>Natalie's - Lemonade</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5</v>
+        <v>10.25</v>
       </c>
       <c r="E15" t="n">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>001025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ithaca Yogurt - Black Cherry</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>14.5</v>
+        <v>10.25</v>
       </c>
     </row>
   </sheetData>
